--- a/GlobalSettings_Data.xlsx
+++ b/GlobalSettings_Data.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="122">
   <si>
     <t>ID</t>
   </si>
@@ -111,12 +111,12 @@
     <t>TC_GS_FUNC_009</t>
   </si>
   <si>
+    <t>DDU</t>
+  </si>
+  <si>
     <t>TC_GS_FUNC_010</t>
   </si>
   <si>
-    <t>DDU</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -138,10 +138,10 @@
     <t>Cost of Goods</t>
   </si>
   <si>
-    <t>Greater than</t>
-  </si>
-  <si>
-    <t>Saudi Arabia</t>
+    <t>Equals</t>
+  </si>
+  <si>
+    <t>Western Sahara</t>
   </si>
   <si>
     <t>TC_GS_FUNC_014</t>
@@ -156,9 +156,6 @@
     <t>Payment Type</t>
   </si>
   <si>
-    <t>Equals</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
@@ -186,6 +183,9 @@
     <t>TC_GS_FUNC_024</t>
   </si>
   <si>
+    <t>Japan</t>
+  </si>
+  <si>
     <t>TC_GS_FUNC_025</t>
   </si>
   <si>
@@ -315,7 +315,7 @@
     <t>TC_GS_FUNC_063</t>
   </si>
   <si>
-    <t>Deactive</t>
+    <t>Inactive</t>
   </si>
   <si>
     <t>TC_GS_FUNC_064</t>
@@ -1678,13 +1678,16 @@
       <c r="A10" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="B10" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>26</v>
@@ -1711,7 +1714,7 @@
         <v>31</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>32</v>
@@ -1728,7 +1731,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>32</v>
@@ -1745,7 +1748,7 @@
         <v>36</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>32</v>
@@ -1762,16 +1765,16 @@
         <v>37</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>38</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>34</v>
@@ -1779,7 +1782,7 @@
     </row>
     <row r="18" ht="28.8" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>27</v>
@@ -1799,7 +1802,7 @@
     </row>
     <row r="19" ht="28.8" spans="1:7">
       <c r="A19" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>27</v>
@@ -1811,10 +1814,10 @@
         <v>38</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>34</v>
@@ -1822,10 +1825,10 @@
     </row>
     <row r="20" ht="28.8" spans="1:7">
       <c r="A20" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>32</v>
@@ -1839,30 +1842,30 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" ht="28.8" spans="1:7">
       <c r="A25" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>32</v>
@@ -1871,7 +1874,7 @@
         <v>33</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" ht="28.8" spans="1:7">
@@ -1879,7 +1882,7 @@
         <v>49</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>32</v>
@@ -1896,7 +1899,7 @@
         <v>50</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>32</v>
@@ -1913,7 +1916,7 @@
         <v>51</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>32</v>
@@ -1930,7 +1933,7 @@
         <v>52</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>32</v>
@@ -1942,19 +1945,37 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" ht="28.8" spans="1:7">
       <c r="A30" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="G30" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" ht="28.8" spans="1:7">
       <c r="A31" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="G31" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" ht="28.8" spans="1:7">
       <c r="A32" s="1" t="s">
         <v>55</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="33" ht="28.8" spans="1:8">
@@ -1962,7 +1983,7 @@
         <v>56</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>32</v>
@@ -1982,7 +2003,7 @@
         <v>57</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>27</v>
@@ -1992,13 +2013,19 @@
       <c r="A35" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="B35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="36" ht="28.8" spans="1:8">
       <c r="A36" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>32</v>
@@ -2015,9 +2042,18 @@
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" ht="28.8" spans="1:8">
       <c r="A38" s="1" t="s">
         <v>61</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -2040,7 +2076,7 @@
         <v>65</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>27</v>
@@ -2167,7 +2203,7 @@
         <v>90</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M63" s="1" t="s">
         <v>82</v>
@@ -2178,7 +2214,7 @@
         <v>91</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M64" s="1" t="s">
         <v>82</v>
@@ -2192,7 +2228,7 @@
         <v>93</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M65" s="1" t="s">
         <v>82</v>
@@ -2282,7 +2318,7 @@
         <v>108</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2290,7 +2326,7 @@
         <v>109</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2298,7 +2334,7 @@
         <v>110</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2306,7 +2342,7 @@
         <v>111</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="84" ht="28.8" spans="1:7">
@@ -2409,9 +2445,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" ht="28.8" spans="1:7">
       <c r="A89" s="1" t="s">
         <v>118</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="90" ht="28.8" spans="1:7">

--- a/GlobalSettings_Data.xlsx
+++ b/GlobalSettings_Data.xlsx
@@ -4,12 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="121">
   <si>
     <t>ID</t>
   </si>
@@ -141,7 +139,7 @@
     <t>Equals</t>
   </si>
   <si>
-    <t>Western Sahara</t>
+    <t>Japan</t>
   </si>
   <si>
     <t>TC_GS_FUNC_014</t>
@@ -181,9 +179,6 @@
   </si>
   <si>
     <t>TC_GS_FUNC_024</t>
-  </si>
-  <si>
-    <t>Japan</t>
   </si>
   <si>
     <t>TC_GS_FUNC_025</t>
@@ -1874,12 +1869,12 @@
         <v>33</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" ht="28.8" spans="1:7">
       <c r="A26" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>24</v>
@@ -1896,7 +1891,7 @@
     </row>
     <row r="27" ht="28.8" spans="1:7">
       <c r="A27" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>24</v>
@@ -1913,7 +1908,7 @@
     </row>
     <row r="28" ht="28.8" spans="1:7">
       <c r="A28" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>24</v>
@@ -1930,7 +1925,7 @@
     </row>
     <row r="29" ht="28.8" spans="1:7">
       <c r="A29" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>24</v>
@@ -1945,17 +1940,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" ht="28.8" spans="1:7">
+    <row r="30" spans="1:7">
       <c r="A30" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" ht="28.8" spans="1:7">
-      <c r="A31" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>34</v>
@@ -1963,7 +1958,7 @@
     </row>
     <row r="32" ht="28.8" spans="1:7">
       <c r="A32" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>24</v>
@@ -1980,7 +1975,7 @@
     </row>
     <row r="33" ht="28.8" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>24</v>
@@ -2000,29 +1995,35 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="G34" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="H34" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="G35" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="H35" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="36" ht="28.8" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>24</v>
@@ -2039,12 +2040,12 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" ht="28.8" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>32</v>
@@ -2058,22 +2059,22 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>24</v>
@@ -2084,7 +2085,7 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>27</v>
@@ -2092,230 +2093,230 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I50" s="2"/>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="M58" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="M58" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="M59" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M60" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="M60" s="1" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="M61" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="M61" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>24</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="64" ht="28.8" spans="1:14">
       <c r="A64" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>24</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65" spans="1:15">
       <c r="A65" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>24</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66" spans="1:15">
       <c r="A66" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="67" spans="1:15">
       <c r="A67" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68" spans="1:15">
       <c r="A68" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="69" spans="1:15">
       <c r="A69" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="70" spans="1:15">
       <c r="A70" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="71" spans="1:15">
       <c r="A71" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="72" spans="1:15">
       <c r="A72" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="73" spans="1:15">
       <c r="A73" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M73" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="74" spans="1:15">
       <c r="A74" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="75" spans="1:15">
       <c r="A75" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76" spans="1:15">
       <c r="A76" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="77" spans="1:15">
       <c r="A77" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="78" spans="1:15">
       <c r="A78" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="79" spans="1:15">
       <c r="A79" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="80" spans="1:15">
       <c r="A80" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>24</v>
@@ -2323,7 +2324,7 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>24</v>
@@ -2331,7 +2332,7 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>24</v>
@@ -2339,7 +2340,7 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>24</v>
@@ -2347,13 +2348,13 @@
     </row>
     <row r="84" ht="28.8" spans="1:7">
       <c r="A84" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>32</v>
@@ -2367,13 +2368,13 @@
     </row>
     <row r="85" ht="28.8" spans="1:7">
       <c r="A85" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>32</v>
@@ -2387,13 +2388,13 @@
     </row>
     <row r="86" ht="28.8" spans="1:7">
       <c r="A86" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>32</v>
@@ -2407,13 +2408,13 @@
     </row>
     <row r="87" ht="28.8" spans="1:7">
       <c r="A87" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>32</v>
@@ -2427,13 +2428,13 @@
     </row>
     <row r="88" ht="28.8" spans="1:7">
       <c r="A88" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>32</v>
@@ -2445,9 +2446,9 @@
         <v>34</v>
       </c>
     </row>
-    <row r="89" ht="28.8" spans="1:7">
+    <row r="89" spans="1:7">
       <c r="A89" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>33</v>
@@ -2458,13 +2459,13 @@
     </row>
     <row r="90" ht="28.8" spans="1:7">
       <c r="A90" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>32</v>
@@ -2478,13 +2479,13 @@
     </row>
     <row r="91" ht="28.8" spans="1:7">
       <c r="A91" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>32</v>
@@ -2498,13 +2499,13 @@
     </row>
     <row r="92" ht="28.8" spans="1:7">
       <c r="A92" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>32</v>
@@ -2520,26 +2521,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>